--- a/app/data/questions.xlsx
+++ b/app/data/questions.xlsx
@@ -416,7 +416,7 @@
   <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>घरों में दूध आमतौर पर किस पशु से मिलता है?</t>
+          <t>घर में दूध देने वाला पालतू पशु कौन-सा है?</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>घोड़ा</t>
+          <t>बंदर</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>सब्ज़ी को पीला रंग देने के लिए कौन-सा मसाला डाला जाता है?</t>
+          <t>सब्ज़ी को पीला रंग देने वाला मसाला कौन-सा है?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -634,32 +634,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>चावल पकाने के लिए सबसे ज़रूरी चीज़ क्या है?</t>
+          <t>पानी उबलने पर ऊपर क्या उठता है?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>तेल</t>
+          <t>धुआँ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>पानी</t>
+          <t>भाप</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>शक्कर</t>
+          <t>राख</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>सिरका</t>
+          <t>बर्फ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>पानी</t>
+          <t>भाप</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -669,32 +669,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>कपड़े धोने के लिए क्या इस्तेमाल किया जाता है?</t>
+          <t>बुखार नापने के लिए क्या इस्तेमाल होता है?</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>चीनी</t>
+          <t>तराज़ू</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>आटा</t>
+          <t>घड़ी</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>दूध</t>
+          <t>थर्मामीटर</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>कपड़े धोने का साबुन</t>
+          <t>फीता</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>कपड़े धोने का साबुन</t>
+          <t>थर्मामीटर</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -709,27 +709,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>कपड़े बनाने के लिए</t>
+          <t>कपड़े</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>गाड़ियाँ और ट्रैक्टर बनाने के लिए</t>
+          <t>गाड़ियाँ और ट्रैक्टर</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>मिठाई बनाने के लिए</t>
+          <t>मिठाई</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>जूते बनाने के लिए</t>
+          <t>जूते</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>गाड़ियाँ और ट्रैक्टर बनाने के लिए</t>
+          <t>गाड़ियाँ और ट्रैक्टर</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -739,32 +739,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>जूठे बर्तन साफ करने के लिए क्या इस्तेमाल होता है?</t>
+          <t>दही किससे जमाई जाती है?</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>मक्खन</t>
+          <t>तेल से</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>घी</t>
+          <t>आटे से</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>दही</t>
+          <t>दूध से</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>बर्तन साफ करने वाला साबुन/लिक्विड</t>
+          <t>पानी से</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>बर्तन साफ करने वाला साबुन/लिक्विड</t>
+          <t>दूध से</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -774,32 +774,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>रसोई गैस सिलेंडर में कौन-सी गैस होती है?</t>
+          <t>आलू कहाँ उगता है?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ऑक्सीजन</t>
+          <t>पेड़ पर</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>एलपीजी</t>
+          <t>ज़मीन के नीचे</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>नाइट्रोजन</t>
+          <t>हवा में</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>हीलियम</t>
+          <t>पानी पर</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>एलपीजी</t>
+          <t>ज़मीन के नीचे</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -809,32 +809,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>पानी उबलने पर ऊपर क्या उठता है?</t>
+          <t>हफ्ते में कितने दिन होते हैं?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>धुआँ</t>
+          <t>पाँच</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>भाप</t>
+          <t>छह</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>राख</t>
+          <t>सात</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>बर्फ</t>
+          <t>आठ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>भाप</t>
+          <t>सात</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -844,32 +844,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>दही किससे जमाया जाता है?</t>
+          <t>बोलेरो किस कंपनी की गाड़ी है?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>तेल से</t>
+          <t>टाटा</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>आटे से</t>
+          <t>मारुति</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>दूध से</t>
+          <t>महिंद्रा</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>पानी से</t>
+          <t>हुंडई</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>दूध से</t>
+          <t>महिंद्रा</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -879,32 +879,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>महिंद्रा का ट्रैक्टर मुख्य रूप से किस काम में आता है?</t>
+          <t>एक रुपये में कितने पैसे होते हैं?</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>खेती में</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>कपड़े सिलने में</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>खाना पकाने में</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>पढ़ाई में</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>खेती में</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -914,32 +914,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>आलू कहाँ उगता है?</t>
+          <t>एक घंटे में कितने मिनट होते हैं?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>पेड़ पर</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ज़मीन के नीचे</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>हवा में</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>पानी के ऊपर</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ज़मीन के नीचे</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -949,32 +949,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>एक हफ्ते में कितने दिन होते हैं?</t>
+          <t>नमक का स्वाद कैसा होता है?</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>पाँच</t>
+          <t>मीठा</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>छह</t>
+          <t>नमकीन</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>सात</t>
+          <t>खट्टा</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>आठ</t>
+          <t>कड़वा</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>सात</t>
+          <t>नमकीन</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -984,32 +984,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>दिवाली पर किसकी पूजा की जाती है?</t>
+          <t>स्कॉर्पियो किस कंपनी की गाड़ी है?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>हनुमान जी</t>
+          <t>महिंद्रा</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>लक्ष्मी-गणेश</t>
+          <t>मारुति</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>सूर्य देव</t>
+          <t>टाटा</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>शनि देव</t>
+          <t>हुंडई</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>लक्ष्मी-गणेश</t>
+          <t>महिंद्रा</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1019,32 +1019,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>रक्षाबंधन पर बहन भाई की कलाई पर क्या बाँधती है?</t>
+          <t>नींबू का स्वाद कैसा होता है?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>राखी</t>
+          <t>मीठा</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>घड़ी</t>
+          <t>कड़वा</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>रुमाल</t>
+          <t>खट्टा</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>कंगन</t>
+          <t>तीखा</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>राखी</t>
+          <t>खट्टा</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1054,32 +1054,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>स्कॉर्पियो किस कंपनी की गाड़ी है?</t>
+          <t>करेले का स्वाद कैसा होता है?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>महिंद्रा</t>
+          <t>मीठा</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>मारुति</t>
+          <t>खट्टा</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>टाटा</t>
+          <t>कड़वा</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>हुंडई</t>
+          <t>नमकीन</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>महिंद्रा</t>
+          <t>कड़वा</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1089,32 +1089,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>करवा चौथ का व्रत महिलाएँ किसके लिए रखती हैं?</t>
+          <t>गुड़ किससे बनता है?</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>बच्चों के रिज़ल्ट के लिए</t>
+          <t>आलू से</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>पति की लंबी उम्र के लिए</t>
+          <t>गन्ने से</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>बारिश के लिए</t>
+          <t>दूध से</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>नौकरी के लिए</t>
+          <t>चावल से</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>पति की लंबी उम्र के लिए</t>
+          <t>गन्ने से</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1124,32 +1124,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>मकर संक्रांति पर आसमान में क्या उड़ाया जाता है?</t>
+          <t>रेलगाड़ी किस पर चलती है?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>गुब्बारा</t>
+          <t>सड़क</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>पतंग</t>
+          <t>पानी</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>हवाई जहाज़</t>
+          <t>पटरी</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>कबूतर</t>
+          <t>हवा</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>पतंग</t>
+          <t>पटरी</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1159,32 +1159,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>होली किस चीज़ का त्योहार है?</t>
+          <t>महिंद्रा का ट्रैक्टर किस काम आता है?</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>दीयों का</t>
+          <t>खेती</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>पतंगों का</t>
+          <t>सिलाई</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>रंगों का</t>
+          <t>खाना पकाना</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>फूलों का</t>
+          <t>पढ़ाई</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>रंगों का</t>
+          <t>खेती</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1194,32 +1194,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>बोलेरो पिक-अप गाड़ी किस काम में आती है?</t>
+          <t>बारिश से बचने के लिए क्या इस्तेमाल करते हैं?</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>सामान ढोने में</t>
+          <t>पंखा</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>कपड़े धोने में</t>
+          <t>छाता</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>खाना बनाने में</t>
+          <t>चश्मा</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>पानी उबालने में</t>
+          <t>चम्मच</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>सामान ढोने में</t>
+          <t>छाता</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1229,32 +1229,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>बुखार नापने के लिए क्या इस्तेमाल होता है?</t>
+          <t>ठंड से बचने के लिए क्या पहनते हैं?</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>थर्मामीटर</t>
+          <t>स्वेटर</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>तराज़ू</t>
+          <t>चप्पल</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>फीता</t>
+          <t>रुमाल</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>घड़ी</t>
+          <t>दुपट्टा</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>थर्मामीटर</t>
+          <t>स्वेटर</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1264,32 +1264,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>कपड़े सिलने के लिए क्या चाहिए?</t>
+          <t>आनंद महिंद्रा किस ग्रुप के चेयरमैन हैं?</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>चाकू-कैंची</t>
+          <t>टाटा</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>सुई-धागा</t>
+          <t>बजाज</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>झाड़ू</t>
+          <t>महिंद्रा</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>कड़छी</t>
+          <t>रिलायंस</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>सुई-धागा</t>
+          <t>महिंद्रा</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1299,32 +1299,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>नमक का स्वाद कैसा होता है?</t>
+          <t>सब्ज़ी काटने के लिए क्या इस्तेमाल होता है?</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>मीठा</t>
+          <t>चाकू</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>नमकीन</t>
+          <t>कंघी</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>खट्टा</t>
+          <t>झाड़ू</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>कड़वा</t>
+          <t>चम्मच</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>नमकीन</t>
+          <t>चाकू</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1334,32 +1334,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>आनंद महिंद्रा किस ग्रुप के चेयरमैन हैं?</t>
+          <t>दाँत साफ़ करने के लिए क्या इस्तेमाल करते हैं?</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>टाटा ग्रुप</t>
+          <t>झाड़ू</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>बजाज ग्रुप</t>
+          <t>ब्रश और पेस्ट</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>महिंद्रा ग्रुप</t>
+          <t>कंघी</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>रिलायंस ग्रुप</t>
+          <t>तौलिया</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>महिंद्रा ग्रुप</t>
+          <t>ब्रश और पेस्ट</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1369,32 +1369,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>नींबू का स्वाद कैसा होता है?</t>
+          <t>कपड़े धोने के लिए क्या इस्तेमाल होता है?</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>खट्टा</t>
+          <t>साबुन</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>मीठा</t>
+          <t>दूध</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>कड़वा</t>
+          <t>आटा</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>तीखा</t>
+          <t>चीनी</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>खट्टा</t>
+          <t>साबुन</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1404,32 +1404,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>करेले का स्वाद कैसा होता है?</t>
+          <t>महिंद्रा का मुख्यालय किस शहर में है?</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>मीठा</t>
+          <t>जयपुर</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>खट्टा</t>
+          <t>मुंबई</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>कड़वा</t>
+          <t>लखनऊ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>नमकीन</t>
+          <t>पटना</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>कड़वा</t>
+          <t>मुंबई</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1439,32 +1439,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>गुड़ किससे बनता है?</t>
+          <t>मोबाइल की बैटरी भरने के लिए क्या लगाते हैं?</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>गन्ने के रस से</t>
+          <t>चार्जर</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>आलू से</t>
+          <t>पंखा</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>दूध से</t>
+          <t>इस्त्री</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>चावल से</t>
+          <t>मिक्सर</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>गन्ने के रस से</t>
+          <t>चार्जर</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1474,32 +1474,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>छत का पंखा किससे चलता है?</t>
+          <t>भारत की राजधानी कौन-सी है?</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>बिजली से</t>
+          <t>मुंबई</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>पानी से</t>
+          <t>कोलकाता</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>हवा से</t>
+          <t>चेन्नई</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>मिट्टी से</t>
+          <t>नई दिल्ली</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>बिजली से</t>
+          <t>नई दिल्ली</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1509,32 +1509,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>फ्रिज का मुख्य काम क्या है?</t>
+          <t>भारत का राष्ट्रीय पशु कौन-सा है?</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>कपड़े सुखाना</t>
+          <t>शेर</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>चीज़ें ठंडी रखना</t>
+          <t>बाघ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>खाना पकाना</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>पानी गरम करना</t>
+          <t>भालू</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>चीज़ें ठंडी रखना</t>
+          <t>बाघ</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1544,32 +1544,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>महिंद्रा का मुख्य कार्यालय किस शहर में है?</t>
+          <t>भारत का राष्ट्रीय पक्षी कौन-सा है?</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>जयपुर</t>
+          <t>तोता</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>मुंबई</t>
+          <t>कबूतर</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>लखनऊ</t>
+          <t>मोर</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>पटना</t>
+          <t>कौआ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>मुंबई</t>
+          <t>मोर</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1579,32 +1579,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>रेलगाड़ी किस पर चलती है?</t>
+          <t>बोलेरो पिक-अप गाड़ी किस काम आती है?</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>सड़क पर</t>
+          <t>सामान ढोने</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>पटरी पर</t>
+          <t>कपड़े धोने</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>पानी पर</t>
+          <t>खाना बनाने</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>हवा में</t>
+          <t>पानी उबालने</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>पटरी पर</t>
+          <t>सामान ढोने</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1614,32 +1614,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>प्रेशर कुकर की सीटी किसके दबाव से बजती है?</t>
+          <t>तिरंगे में सबसे ऊपर कौन-सा रंग होता है?</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>भाप</t>
+          <t>हरा</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>बिजली</t>
+          <t>सफेद</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>पानी की बूँद</t>
+          <t>केसरिया</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>तेल</t>
+          <t>नीला</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>भाप</t>
+          <t>केसरिया</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -1649,27 +1649,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>इनमें से कौन-सा फल है?</t>
+          <t>भारत का राष्ट्रीय फल कौन-सा है?</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>आलू</t>
+          <t>केला</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>प्याज</t>
+          <t>आम</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>गोभी</t>
+          <t>सेब</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>आम</t>
+          <t>अंगूर</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1684,7 +1684,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>इनमें से कौन-सी पत्तेदार सब्ज़ी है?</t>
+          <t>समोसे में आमतौर पर क्या भरा जाता है?</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>प्याज</t>
+          <t>चीनी</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>पालक</t>
+          <t>चावल</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>अदरक</t>
+          <t>दूध</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>पालक</t>
+          <t>आलू</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1719,32 +1719,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>थार गाड़ी किस तरह के रास्तों के लिए मशहूर है?</t>
+          <t>इडली किस क्षेत्र का मशहूर नाश्ता है?</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>सिर्फ़ चिकनी सड़क के लिए</t>
+          <t>कश्मीर</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>पहाड़ी और ऊबड़-खाबड़ रास्तों के लिए</t>
+          <t>राजस्थान</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>पानी के रास्तों के लिए</t>
+          <t>दक्षिण भारत</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>रेल की पटरी के लिए</t>
+          <t>असम</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>पहाड़ी और ऊबड़-खाबड़ रास्तों के लिए</t>
+          <t>दक्षिण भारत</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1754,32 +1754,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>मोबाइल की बैटरी भरने के लिए क्या लगाते हैं?</t>
+          <t>थार किस तरह की गाड़ी है?</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>चार्जर</t>
+          <t>साइकिल</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>पंखा</t>
+          <t>ऑफ-रोड एसयूवी</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>इस्त्री</t>
+          <t>ट्रेन</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>मिक्सर</t>
+          <t>स्कूटर</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>चार्जर</t>
+          <t>ऑफ-रोड एसयूवी</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1789,32 +1789,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>फैक्ट्री में काम करते समय सिर की सुरक्षा के लिए क्या पहनना चाहिए?</t>
+          <t>तड़का लगाने के लिए क्या गरम करते हैं?</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>दुपट्टा</t>
+          <t>दूध</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>चश्मा</t>
+          <t>पानी</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>दस्ताने</t>
+          <t>तेल</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>हेलमेट</t>
+          <t>आटा</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>हेलमेट</t>
+          <t>तेल</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -1824,32 +1824,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>इडली किस क्षेत्र का मशहूर नाश्ता है?</t>
+          <t>फ्रिज का मुख्य काम क्या है?</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>कश्मीर</t>
+          <t>कपड़े सुखाना</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>दक्षिण भारत</t>
+          <t>चीज़ें ठंडी रखना</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>राजस्थान</t>
+          <t>खाना पकाना</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>असम</t>
+          <t>पानी गरम करना</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>दक्षिण भारत</t>
+          <t>चीज़ें ठंडी रखना</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -1859,32 +1859,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>समोसे में आमतौर पर क्या भरा जाता है?</t>
+          <t>छत का पंखा किससे चलता है?</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>आलू</t>
+          <t>बिजली</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>चीनी</t>
+          <t>पानी</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>चावल</t>
+          <t>हवा</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>दूध</t>
+          <t>मिट्टी</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>आलू</t>
+          <t>बिजली</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -1894,32 +1894,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>बच्चे स्कूल जाते समय पीठ पर क्या टाँगते हैं?</t>
+          <t>फैक्ट्री में सिर की सुरक्षा के लिए क्या पहनते हैं?</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>बस्ता</t>
+          <t>दुपट्टा</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>तकिया</t>
+          <t>चश्मा</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>थाली</t>
+          <t>दस्ताने</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>बाल्टी</t>
+          <t>हेलमेट</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>बस्ता</t>
+          <t>हेलमेट</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -1929,32 +1929,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>हम कानों से क्या करते हैं?</t>
+          <t>रसोई गैस सिलेंडर में कौन-सी गैस होती है?</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>देखते हैं</t>
+          <t>ऑक्सीजन</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>सुनते हैं</t>
+          <t>एलपीजी</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>सूँघते हैं</t>
+          <t>नाइट्रोजन</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>चखते हैं</t>
+          <t>हीलियम</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>सुनते हैं</t>
+          <t>एलपीजी</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -1964,32 +1964,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>रात को सोने के लिए क्या बिछाते हैं?</t>
+          <t>स्कूल जाते समय बच्चे पीठ पर क्या टाँगते हैं?</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>चूल्हा</t>
+          <t>बस्ता</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>कड़ाही</t>
+          <t>तकिया</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>बिस्तर</t>
+          <t>थाली</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>झाड़ू</t>
+          <t>बाल्टी</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>बिस्तर</t>
+          <t>बस्ता</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1999,32 +1999,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>भारत की राजधानी कौन-सी है?</t>
+          <t>एक दर्जन में कितनी चीज़ें होती हैं?</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>मुंबई</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>कोलकाता</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>चेन्नई</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>नई दिल्ली</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>नई दिल्ली</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2034,32 +2034,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>तिरंगे में सबसे ऊपर कौन-सा रंग होता है?</t>
+          <t>आधा किलो में कितने ग्राम होते हैं?</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>हरा</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>सफेद</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>केसरिया</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>नीला</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>केसरिया</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2069,32 +2069,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>भारत का राष्ट्रीय पशु कौन-सा है?</t>
+          <t>घड़ी में छोटी सुई क्या बताती है?</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>शेर</t>
+          <t>घंटे</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>बाघ</t>
+          <t>सेकंड</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>मिनट</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>भालू</t>
+          <t>दिन</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>बाघ</t>
+          <t>घंटे</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2104,32 +2104,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>एक रुपये में कितने पैसे होते हैं?</t>
+          <t>सूरज किस दिशा में उगता है?</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>पश्चिम</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>उत्तर</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>पूरब</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>दक्षिण</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>पूरब</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2139,32 +2139,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>एक घंटे में कितने मिनट होते हैं?</t>
+          <t>पानी जमने पर क्या बनता है?</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>भाप</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>बर्फ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>धुआँ</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>राख</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>बर्फ</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2174,32 +2174,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>बोलेरो क्या है?</t>
+          <t>रात को आसमान में क्या चमकता है?</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>गाड़ी</t>
+          <t>चाँद</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>मिक्सर</t>
+          <t>इंद्रधनुष</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>पंखा</t>
+          <t>बादल</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>टीवी</t>
+          <t>बिजली का पंखा</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>गाड़ी</t>
+          <t>चाँद</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2209,32 +2209,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>बासमती चावल किस चीज़ के लिए मशहूर है?</t>
+          <t>पनीर किससे बनता है?</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>लाल रंग</t>
+          <t>आटे से</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>खुशबू और लंबे दाने</t>
+          <t>दूध से</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>मोटे गोल दाने</t>
+          <t>बेसन से</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>खट्टे स्वाद</t>
+          <t>चावल से</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>खुशबू और लंबे दाने</t>
+          <t>दूध से</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2249,27 +2249,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>मूंग दाल</t>
+          <t>मूंग</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>अरहर दाल</t>
+          <t>उड़द</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>चने की दाल</t>
+          <t>चना</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>उड़द दाल</t>
+          <t>अरहर</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>चने की दाल</t>
+          <t>चना</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2279,7 +2279,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>पनीर किससे बनता है?</t>
+          <t>घी किससे बनता है?</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2289,22 +2289,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>दूध से</t>
+          <t>मलाई/मक्खन से</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>बेसन से</t>
+          <t>चीनी से</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>चावल से</t>
+          <t>पानी से</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>दूध से</t>
+          <t>मलाई/मक्खन से</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2314,32 +2314,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>घी किससे बनाया जाता है?</t>
+          <t>लाल-नारंगी रंग की दाल कौन-सी है?</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>आटे से</t>
+          <t>चना</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>मलाई/मक्खन से</t>
+          <t>उड़द</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>पानी से</t>
+          <t>मसूर</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>शक्कर से</t>
+          <t>अरहर</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>मलाई/मक्खन से</t>
+          <t>मसूर</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2349,32 +2349,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>इनमें से किस दाल का रंग नारंगी-लाल होता है?</t>
+          <t>दाल के तड़के में खुशबू के लिए क्या डालते हैं?</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>चना दाल</t>
+          <t>चीनी</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>उड़द दाल</t>
+          <t>जीरा-हींग</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>मसूर दाल</t>
+          <t>दूध</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>अरहर दाल</t>
+          <t>आटा</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>मसूर दाल</t>
+          <t>जीरा-हींग</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2384,7 +2384,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>दाल के तड़के में खुशबू के लिए आमतौर पर क्या डाला जाता है?</t>
+          <t>इनमें से कौन-सा साबुत गरम मसाला है?</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2394,22 +2394,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>जीरा-हींग</t>
+          <t>मैदा</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>दूध</t>
+          <t>लौंग</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>आटा</t>
+          <t>सूजी</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>जीरा-हींग</t>
+          <t>लौंग</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2419,32 +2419,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>इनमें से कौन-सा साबुत गरम मसाला है?</t>
+          <t>पानी को कीटाणुमुक्त करने का आसान तरीका?</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>चीनी</t>
+          <t>उबालना</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>मैदा</t>
+          <t>जमाना</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>लौंग</t>
+          <t>चीनी मिलाना</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>सूजी</t>
+          <t>छानना</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>लौंग</t>
+          <t>उबालना</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2454,32 +2454,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>पीने के पानी को कीटाणुमुक्त करने का सबसे आसान घरेलू तरीका क्या है?</t>
+          <t>दस्त में पानी की कमी रोकने के लिए क्या देते हैं?</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>पानी में चीनी मिलाना</t>
+          <t>चाय</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>पानी उबालना</t>
+          <t>ओआरएस</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>पानी जमाना</t>
+          <t>कॉफ़ी</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>पानी धूप में रखना</t>
+          <t>कोल्ड ड्रिंक</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>पानी उबालना</t>
+          <t>ओआरएस</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2489,32 +2489,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>बच्चों को पोलियो से बचाने के लिए क्या पिलाया जाता है?</t>
+          <t>बोलेरो, स्कॉर्पियो और थार किस कंपनी की हैं?</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>काढ़ा</t>
+          <t>टाटा</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ग्लूकोज़</t>
+          <t>महिंद्रा</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>दो बूँद पोलियो की दवा</t>
+          <t>मारुति</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>शहद</t>
+          <t>हुंडई</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>दो बूँद पोलियो की दवा</t>
+          <t>महिंद्रा</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2524,32 +2524,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>दस्त में शरीर में पानी की कमी रोकने के लिए क्या दिया जाता है?</t>
+          <t>हड्डियाँ मज़बूत करने के लिए क्या अच्छा है?</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>दूध</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>चाय</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ओआरएस घोल</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>कॉफ़ी</t>
+          <t>चीनी</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>कोल्ड ड्रिंक</t>
+          <t>नमक</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ओआरएस घोल</t>
+          <t>दूध</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -2559,32 +2559,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>बोलेरो, स्कॉर्पियो और थार ये तीनों किस कंपनी की गाड़ियाँ हैं?</t>
+          <t>खून बढ़ाने के लिए कौन-सी सब्ज़ी अच्छी है?</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>टाटा</t>
+          <t>लौकी</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>महिंद्रा</t>
+          <t>खीरा</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>मारुति</t>
+          <t>पालक</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>हुंडई</t>
+          <t>मूली</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>महिंद्रा</t>
+          <t>पालक</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -2594,32 +2594,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>हड्डियाँ मज़बूत करने के लिए कैल्शियम किसमें भरपूर होता है?</t>
+          <t>विटामिन C सबसे ज़्यादा किसमें होता है?</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>दूध</t>
+          <t>आलू</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>चाय</t>
+          <t>चावल</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>चीनी</t>
+          <t>आँवला</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>नमक</t>
+          <t>आटा</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>दूध</t>
+          <t>आँवला</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -2629,32 +2629,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>खून बढ़ाने के लिए कौन-सी सब्ज़ी अच्छी मानी जाती है?</t>
+          <t>गैस की महक आए तो सबसे पहले क्या करें?</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>लौकी</t>
+          <t>माचिस जलाएँ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>खीरा</t>
+          <t>स्विच दबाएँ</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>पालक</t>
+          <t>पंखा चलाएँ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>मूली</t>
+          <t>रेगुलेटर बंद करें</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>पालक</t>
+          <t>रेगुलेटर बंद करें</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -2664,32 +2664,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>विटामिन C सबसे ज़्यादा किसमें मिलता है?</t>
+          <t>क्लब महिंद्रा किससे जुड़ा है?</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>आलू</t>
+          <t>छुट्टियाँ और रिसॉर्ट</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>चावल</t>
+          <t>स्कूल</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>आँवला</t>
+          <t>बैंक</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>आटा</t>
+          <t>अस्पताल</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>आँवला</t>
+          <t>छुट्टियाँ और रिसॉर्ट</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -2699,32 +2699,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>रसोई में गैस की महक आए तो सबसे पहले क्या करना चाहिए?</t>
+          <t>पैसे जमा-निकालने के लिए कौन-सा खाता खुलवाते हैं?</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>माचिस जलाना</t>
+          <t>चाय खाता</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>बिजली का स्विच दबाना</t>
+          <t>दूध खाता</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>पंखा चलाना</t>
+          <t>बचत खाता</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>रेगुलेटर बंद करके खिड़कियाँ खोलना</t>
+          <t>कपड़ा खाता</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>रेगुलेटर बंद करके खिड़कियाँ खोलना</t>
+          <t>बचत खाता</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -2734,32 +2734,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>घर में आग लग जाए तो दमकल का नंबर क्या है?</t>
+          <t>यूपीआई से क्या किया जा सकता है?</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>मोबाइल से पैसे भेजना</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>गाड़ी चलाना</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>खाना पकाना</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>कपड़े धोना</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>मोबाइल से पैसे भेजना</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -2769,32 +2769,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>राशन कार्ड से मुख्य रूप से क्या मिलता है?</t>
+          <t>बिजली का बिल कम करने वाला बल्ब कौन-सा है?</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>बिजली</t>
+          <t>एलईडी</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>मोबाइल</t>
+          <t>फिलामेंट</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>सस्ता अनाज/राशन</t>
+          <t>लालटेन</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>गाड़ी</t>
+          <t>मोमबत्ती</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>सस्ता अनाज/राशन</t>
+          <t>एलईडी</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -2804,32 +2804,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>आधार कार्ड में कितने अंक होते हैं?</t>
+          <t>कपड़ों की सिलवटें हटाने के लिए क्या लेते हैं?</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>मिक्सर</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>कुकर</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>इस्त्री</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>पंखा</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>इस्त्री</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -2839,32 +2839,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>स्कॉर्पियो का हिंदी में क्या मतलब होता है?</t>
+          <t>मिक्सर-ग्राइंडर का काम क्या है?</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>बिच्छू</t>
+          <t>कपड़े सुखाना</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>शेर</t>
+          <t>पानी गरम करना</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>हाथी</t>
+          <t>मसाला पीसना</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>साँप</t>
+          <t>कमरा ठंडा करना</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>बिच्छू</t>
+          <t>मसाला पीसना</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -2874,32 +2874,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>पैसे जमा करने और निकालने के लिए बैंक में कौन-सा खाता खुलवाते हैं?</t>
+          <t>माइक्रोवेव में कौन-सा बर्तन नहीं रखना चाहिए?</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>बचत खाता</t>
+          <t>काँच का कटोरा</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>चाय खाता</t>
+          <t>धातु का बर्तन</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>दूध खाता</t>
+          <t>सिरेमिक कटोरी</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>कपड़ा खाता</t>
+          <t>माइक्रोवेव-सेफ प्लेट</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>बचत खाता</t>
+          <t>धातु का बर्तन</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -2909,32 +2909,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>यूपीआई (UPI) से क्या किया जा सकता है?</t>
+          <t>दुनिया में सबसे ज़्यादा संख्या में महिंद्रा क्या बनाती है?</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>गाड़ी चलाना</t>
+          <t>ट्रैक्टर</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>मोबाइल से पैसे भेजना</t>
+          <t>साइकिल</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>खाना पकाना</t>
+          <t>मोबाइल</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>कपड़े धोना</t>
+          <t>हवाई जहाज़</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>मोबाइल से पैसे भेजना</t>
+          <t>ट्रैक्टर</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -2944,32 +2944,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>बिजली का बिल कम करने के लिए कौन-सा बल्ब बेहतर है?</t>
+          <t>नॉन-स्टिक कड़ाही में कौन-सा चम्मच चलाएँ?</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>एलईडी बल्ब</t>
+          <t>लोहे का</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>पुराना फिलामेंट बल्ब</t>
+          <t>स्टील का</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>लालटेन</t>
+          <t>लकड़ी का</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>मोमबत्ती</t>
+          <t>चाकू</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>एलईडी बल्ब</t>
+          <t>लकड़ी का</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -2979,32 +2979,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>क्लब महिंद्रा किस काम से जुड़ा है?</t>
+          <t>इनमें कौन-सी कंपनी महिंद्रा ग्रुप की नहीं है?</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>छुट्टियाँ और रिसॉर्ट</t>
+          <t>टेक महिंद्रा</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>स्कूल की किताबें</t>
+          <t>क्लब महिंद्रा</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>बैंक</t>
+          <t>महिंद्रा फाइनेंस</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>अस्पताल</t>
+          <t>इन्फोसिस</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>छुट्टियाँ और रिसॉर्ट</t>
+          <t>इन्फोसिस</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -3014,32 +3014,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>कपड़ों की सिलवटें हटाने के लिए क्या इस्तेमाल होता है?</t>
+          <t>दूध उबलते समय बाहर क्यों गिरता है?</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>मिक्सर</t>
+          <t>भाप के उफान से</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>इस्त्री</t>
+          <t>नमक से</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>कुकर</t>
+          <t>चीनी से</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>पंखा</t>
+          <t>पंखे से</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>इस्त्री</t>
+          <t>भाप के उफान से</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -3049,32 +3049,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>मिक्सर-ग्राइंडर का मुख्य काम क्या है?</t>
+          <t>सफेद कपड़ों में चमक के लिए क्या डालते हैं?</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>मसाले और चटनी पीसना</t>
+          <t>नील</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>कपड़े सुखाना</t>
+          <t>नमक</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>पानी गरम करना</t>
+          <t>चीनी</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>कमरा ठंडा करना</t>
+          <t>तेल</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>मसाले और चटनी पीसना</t>
+          <t>नील</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -3084,32 +3084,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>माइक्रोवेव ओवन में कौन-सा बर्तन नहीं रखना चाहिए?</t>
+          <t>घर के पानी को साफ़ करने का उपकरण?</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>काँच का कटोरा</t>
+          <t>मिक्सर</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>माइक्रोवेव-सेफ प्लेट</t>
+          <t>इस्त्री</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>धातु (स्टील/एल्युमिनियम) का बर्तन</t>
+          <t>वाटर फ़िल्टर</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>सिरेमिक कटोरी</t>
+          <t>पंखा</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>धातु (स्टील/एल्युमिनियम) का बर्तन</t>
+          <t>वाटर फ़िल्टर</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -3119,32 +3119,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>महिंद्रा को किस मामले में दुनिया की सबसे बड़ी कंपनियों में गिना जाता है?</t>
+          <t>तड़के के लिए तेल कैसा होना चाहिए?</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ट्रैक्टर की बिक्री में</t>
+          <t>ठंडा</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>कपड़ों की बिक्री में</t>
+          <t>गरम</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>मिठाई की बिक्री में</t>
+          <t>जमा हुआ</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>जूतों की बिक्री में</t>
+          <t>बर्फ जैसा</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ट्रैक्टर की बिक्री में</t>
+          <t>गरम</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -3154,32 +3154,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>नॉन-स्टिक कड़ाही में चलाने के लिए कौन-सा चम्मच बेहतर है?</t>
+          <t>थार नाम किस रेगिस्तान पर रखा गया है?</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>लोहे का</t>
+          <t>सहारा</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>स्टील का नुकीला</t>
+          <t>गोबी</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>लकड़ी का</t>
+          <t>थार</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>चाकू</t>
+          <t>कच्छ का रण</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>लकड़ी का</t>
+          <t>थार</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3189,32 +3189,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>नवरात्रि कितने दिनों तक मनाई जाती है?</t>
+          <t>फल खरीदते समय सबसे ज़रूरी बात क्या देखें?</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>बहुत बड़ा हो</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>ताज़ा हो</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>चमकीला स्टिकर</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>बहुत पुराना</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>ताज़ा हो</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -3224,32 +3224,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>गणेश चतुर्थी किस देवता का त्योहार है?</t>
+          <t>प्याज़ काटते समय आँखों में पानी क्यों आता है?</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>गणपति</t>
+          <t>नमक से</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>हनुमान जी</t>
+          <t>चाकू से</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>शिव जी</t>
+          <t>प्याज़ के रसायन से</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>सूर्य देव</t>
+          <t>पानी से</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>गणपति</t>
+          <t>प्याज़ के रसायन से</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -3259,32 +3259,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ईद पर घरों में कौन-सी मीठी चीज़ ख़ास तौर पर बनती है?</t>
+          <t>स्वराज ट्रैक्टर किस ग्रुप का हिस्सा है?</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>सेवइयाँ</t>
+          <t>टाटा</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>जलेबी</t>
+          <t>बजाज</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>पूरनपोली</t>
+          <t>मारुति</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>गुजिया</t>
+          <t>महिंद्रा</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>सेवइयाँ</t>
+          <t>महिंद्रा</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -3294,32 +3294,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>एक्सयूवी700 क्या है?</t>
+          <t>ढोकला किस राज्य का मशहूर व्यंजन है?</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ट्रैक्टर</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>एसयूवी गाड़ी</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>साइकिल</t>
+          <t>केरल</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ट्रेन</t>
+          <t>बिहार</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>एसयूवी गाड़ी</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -3329,32 +3329,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>क्रिसमस किस तारीख को मनाया जाता है?</t>
+          <t>सरसों का साग और मक्के की रोटी किस राज्य की पहचान है?</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>25 दिसंबर</t>
+          <t>तमिलनाडु</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1 जनवरी</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>15 अगस्त</t>
+          <t>केरल</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2 अक्टूबर</t>
+          <t>ओडिशा</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>25 दिसंबर</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -3364,32 +3364,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>दशहरे पर किसका पुतला जलाया जाता है?</t>
+          <t>वड़ा पाव किस राज्य का मशहूर स्ट्रीट फूड है?</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>कंस का</t>
+          <t>महाराष्ट्र</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>रावण का</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>हिरण्यकश्यप का</t>
+          <t>बिहार</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>शकुनि का</t>
+          <t>असम</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>रावण का</t>
+          <t>महाराष्ट्र</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -3399,32 +3399,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>गाँधी जयंती किस तारीख को मनाई जाती है?</t>
+          <t>लिट्टी-चोखा किस राज्य की पहचान है?</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2 अक्टूबर</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>15 अगस्त</t>
+          <t>बिहार</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>26 जनवरी</t>
+          <t>केरल</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>14 नवंबर</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2 अक्टूबर</t>
+          <t>बिहार</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -3434,32 +3434,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>भारत का स्वतंत्रता दिवस कब मनाया जाता है?</t>
+          <t>इडली का घोल किन दो चीज़ों से बनता है?</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>26 जनवरी</t>
+          <t>गेहूँ-चना</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2 अक्टूबर</t>
+          <t>चावल-उड़द दाल</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>15 अगस्त</t>
+          <t>मक्का-मूंग</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1 मई</t>
+          <t>बाजरा-तिल</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>15 अगस्त</t>
+          <t>चावल-उड़द दाल</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -3469,32 +3469,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>गणतंत्र दिवस कब मनाया जाता है?</t>
+          <t>महाराष्ट्र की राजधानी कौन-सी है?</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>26 जनवरी</t>
+          <t>पुणे</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>15 अगस्त</t>
+          <t>नागपुर</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5 सितंबर</t>
+          <t>मुंबई</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>14 नवंबर</t>
+          <t>नासिक</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>26 जनवरी</t>
+          <t>मुंबई</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -3504,32 +3504,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>इनमें से कौन-सी कंपनी महिंद्रा ग्रुप की नहीं है?</t>
+          <t>स्वतंत्रता दिवस कब मनाया जाता है?</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>टेक महिंद्रा</t>
+          <t>26 जनवरी</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>क्लब महिंद्रा</t>
+          <t>2 अक्टूबर</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>महिंद्रा फाइनेंस</t>
+          <t>15 अगस्त</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>इन्फोसिस</t>
+          <t>1 मई</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>इन्फोसिस</t>
+          <t>15 अगस्त</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -3539,32 +3539,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>महाराष्ट्र की राजधानी कौन-सी है?</t>
+          <t>गणतंत्र दिवस कब मनाया जाता है?</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>पुणे</t>
+          <t>26 जनवरी</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>नागपुर</t>
+          <t>15 अगस्त</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>मुंबई</t>
+          <t>5 सितंबर</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>नासिक</t>
+          <t>14 नवंबर</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>मुंबई</t>
+          <t>26 जनवरी</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -3574,32 +3574,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>महाराष्ट्र का मशहूर स्ट्रीट फूड कौन-सा है?</t>
+          <t>गाँधी जयंती किस तारीख को आती है?</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>वड़ा पाव</t>
+          <t>2 अक्टूबर</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ढोकला</t>
+          <t>15 अगस्त</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>इडली</t>
+          <t>26 जनवरी</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>छोले-भटूरे</t>
+          <t>14 नवंबर</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>वड़ा पाव</t>
+          <t>2 अक्टूबर</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -3609,32 +3609,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>गणपति बप्पा को कौन-सी मिठाई सबसे प्रिय मानी जाती है?</t>
+          <t>पौन किलो कितने ग्राम का होता है?</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>रसगुल्ला</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>मोदक</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>जलेबी</t>
+          <t>750</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>बर्फी</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>मोदक</t>
+          <t>750</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -3644,32 +3644,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ढोकला किस राज्य का मशहूर व्यंजन है?</t>
+          <t>एक किलो में कितने ग्राम होते हैं?</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>केरल</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>बिहार</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -3679,32 +3679,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>सरसों का साग और मक्के की रोटी किस राज्य की पहचान है?</t>
+          <t>सब्ज़ी में नमक ज़्यादा हो जाए तो क्या मिलाएँ?</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>तमिलनाडु</t>
+          <t>उबला आलू</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>मिर्च</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>केरल</t>
+          <t>चीनी</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ओडिशा</t>
+          <t>हल्दी</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>उबला आलू</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -3714,32 +3714,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>पूरनपोली किस राज्य का पारंपरिक पकवान है?</t>
+          <t>स्कॉर्पियो का हिंदी में मतलब क्या है?</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>महाराष्ट्र</t>
+          <t>बिच्छू</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>असम</t>
+          <t>शेर</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>हाथी</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>बंगाल</t>
+          <t>साँप</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>महाराष्ट्र</t>
+          <t>बिच्छू</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -3749,32 +3749,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>इडली का घोल किन दो चीज़ों से बनता है?</t>
+          <t>टेक महिंद्रा किस क्षेत्र की कंपनी है?</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>गेहूँ और चना</t>
+          <t>कपड़ा</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>चावल और उड़द दाल</t>
+          <t>मिठाई</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>मक्का और मूंग</t>
+          <t>आईटी</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>बाजरा और तिल</t>
+          <t>जूते</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>चावल और उड़द दाल</t>
+          <t>आईटी</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -3784,32 +3784,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>बोलेरो अपनी किस खूबी के लिए गाँव-शहर में मशहूर है?</t>
+          <t>महिंद्रा फाइनेंस क्या सुविधा देती है?</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>मज़बूती और टिकाऊपन</t>
+          <t>मुफ़्त राशन</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>छोटे आकार के लिए</t>
+          <t>लोन</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>उड़ने की क्षमता के लिए</t>
+          <t>बिजली</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>पानी पर चलने के लिए</t>
+          <t>किताबें</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>मज़बूती और टिकाऊपन</t>
+          <t>लोन</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -3819,32 +3819,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>थार नाम की गाड़ी का नाम किस रेगिस्तान पर रखा गया है?</t>
+          <t>इनमें कौन-सी चीज़ महिंद्रा नहीं बनाती?</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>थार रेगिस्तान</t>
+          <t>ट्रैक्टर</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>सहारा रेगिस्तान</t>
+          <t>एसयूवी</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>गोबी रेगिस्तान</t>
+          <t>मोबाइल फ़ोन</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>कच्छ का रण</t>
+          <t>पिक-अप</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>थार रेगिस्तान</t>
+          <t>मोबाइल फ़ोन</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -3854,32 +3854,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>महिंद्रा फाइनेंस मुख्य रूप से क्या सुविधा देती है?</t>
+          <t>रोटी बेलते समय आटा चिपके तो क्या लगाते हैं?</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>गाड़ी और ट्रैक्टर के लिए लोन</t>
+          <t>पानी</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>मुफ़्त राशन</t>
+          <t>दूध</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>स्कूल की किताबें</t>
+          <t>तेल</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>बिजली कनेक्शन</t>
+          <t>सूखा आटा</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>गाड़ी और ट्रैक्टर के लिए लोन</t>
+          <t>सूखा आटा</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -3889,32 +3889,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>इनमें से कौन-सी चीज़ महिंद्रा नहीं बनाती?</t>
+          <t>सब्ज़ी धोने का सबसे सही तरीका?</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ट्रैक्टर</t>
+          <t>बहते पानी में</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>एसयूवी</t>
+          <t>गरम तेल में</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>मोबाइल फ़ोन</t>
+          <t>दूध में</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>पिक-अप ट्रक</t>
+          <t>चीनी के पानी में</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>मोबाइल फ़ोन</t>
+          <t>बहते पानी में</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -3924,32 +3924,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>सब्ज़ी में नमक ज़्यादा हो जाए तो उसमें क्या मिलाने से स्वाद ठीक हो सकता है?</t>
+          <t>आटा-दाल में कीड़े न लगें, इसके लिए कहाँ रखें?</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ज़्यादा नमक</t>
+          <t>खुली थैली में</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>मिर्च पाउडर</t>
+          <t>गीली जगह</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>उबला आलू</t>
+          <t>बंद सूखे डिब्बे में</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>हल्दी</t>
+          <t>धूप में</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>उबला आलू</t>
+          <t>बंद सूखे डिब्बे में</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -3959,32 +3959,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>आटा 36 रुपये किलो है, तो ढाई किलो आटे का दाम कितना होगा?</t>
+          <t>सेब काटकर रखने पर भूरा क्यों पड़ता है?</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>80 रुपये</t>
+          <t>हवा के असर से</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>90 रुपये</t>
+          <t>ठंड से</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>100 रुपये</t>
+          <t>रोशनी से</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>72 रुपये</t>
+          <t>नमी से</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>90 रुपये</t>
+          <t>हवा के असर से</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -3994,32 +3994,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>दाल 160 रुपये किलो है, तो 750 ग्राम दाल का दाम कितना होगा?</t>
+          <t>एलपीजी गैस में गंध अलग से क्यों मिलाई जाती है?</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>100 रुपये</t>
+          <t>ताकि लीक होने पर पता चले</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>110 रुपये</t>
+          <t>ताकि गैस सस्ती हो</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>120 रुपये</t>
+          <t>ताकि रंग आए</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>130 रुपये</t>
+          <t>ताकि ज़्यादा जले</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>120 रुपये</t>
+          <t>ताकि लीक होने पर पता चले</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -4029,32 +4029,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>रोज़ पौन लीटर दूध आता है, तो 30 दिन में कुल कितना दूध आएगा?</t>
+          <t>कटे आलू को पानी में क्यों रखते हैं?</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>20 लीटर</t>
+          <t>मीठे हो जाएँ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>22.5 लीटर</t>
+          <t>काले न पड़ें</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>25 लीटर</t>
+          <t>जल्दी गलें</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>30 लीटर</t>
+          <t>सख़्त हो जाएँ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>22.5 लीटर</t>
+          <t>काले न पड़ें</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -4064,32 +4064,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>घर में 5 लोग हैं और हर कोई रोज़ 2 रोटी खाता है, तो एक हफ्ते में कुल कितनी रोटियाँ बनेंगी?</t>
+          <t>चावल पकाने से पहले धोने का कारण?</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>रंग बदलना</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>वज़न बढ़ाना</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>गंदगी हटाना</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>स्वाद कड़वा करना</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>गंदगी हटाना</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -4099,32 +4099,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>एक दर्जन अंडे 84 रुपये के हैं, तो एक अंडे का दाम कितना हुआ?</t>
+          <t>गैस चूल्हे की नीली लौ क्या बताती है?</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>6 रुपये</t>
+          <t>गैस लीक</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7 रुपये</t>
+          <t>पूरा जलना</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>8 रुपये</t>
+          <t>सिलेंडर खाली</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>9 रुपये</t>
+          <t>बर्नर खराब</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>7 रुपये</t>
+          <t>पूरा जलना</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -4134,32 +4134,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>20% छूट के बाद साड़ी 800 रुपये की पड़ी, तो उसका असली दाम कितना था?</t>
+          <t>कौन-सी चीज़ बिना भिगोए जल्दी गल जाती है?</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>960 रुपये</t>
+          <t>राजमा</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>1000 रुपये</t>
+          <t>काले चने</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1040 रुपये</t>
+          <t>मसूर दाल</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1200 रुपये</t>
+          <t>साबुत उड़द</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1000 रुपये</t>
+          <t>मसूर दाल</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -4169,32 +4169,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>बिजली मीटर में पिछला रीडिंग 1250 था और अब 1340 है। एक यूनिट 6 रुपये की हो तो बिल कितना बनेगा?</t>
+          <t>आलू हरे पड़ जाएँ तो क्या करें?</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>450 रुपये</t>
+          <t>वैसे ही पकाएँ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>540 रुपये</t>
+          <t>ज़्यादा नमक डालें</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>600 रुपये</t>
+          <t>हरा हिस्सा काटकर फेंकें</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>720 रुपये</t>
+          <t>धूप में रखें</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>540 रुपये</t>
+          <t>हरा हिस्सा काटकर फेंकें</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -4204,32 +4204,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1000 रुपये के सामान पर 5% छूट मिले तो कितने रुपये देने होंगे?</t>
+          <t>ताज़ा अंडा पानी में डालने पर क्या होता है?</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>ऊपर तैरता है</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>तली में बैठता है</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>घुल जाता है</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>गरम होता है</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>तली में बैठता है</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -4239,32 +4239,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>घरेलू गैस सिलेंडर में आमतौर पर कितने किलो गैस होती है?</t>
+          <t>शहद जम जाए तो इसका मतलब आमतौर पर क्या होता है?</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5 किलो</t>
+          <t>ज़रूर नकली है</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>10 किलो</t>
+          <t>वह असली हो सकता है</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>14.2 किलो</t>
+          <t>खराब हो गया</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>25 किलो</t>
+          <t>उसमें चीनी है</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>14.2 किलो</t>
+          <t>वह असली हो सकता है</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -4274,32 +4274,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>चावल उबालकर पकाते समय 1 कप चावल के लिए लगभग कितना पानी चाहिए होता है?</t>
+          <t>मिट्टी का घड़ा पानी ठंडा क्यों रखता है?</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>आधा कप</t>
+          <t>उसमें बर्फ है</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1 कप</t>
+          <t>रंग लाल है</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2 कप</t>
+          <t>छेदों से भाप बनती है</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>5 कप</t>
+          <t>आकार गोल है</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2 कप</t>
+          <t>छेदों से भाप बनती है</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -4309,32 +4309,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>रोटी तवे पर फूलती किसकी वजह से है?</t>
+          <t>प्रेशर कुकर का ढक्कन कब खोलें?</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>अंदर बनी भाप की वजह से</t>
+          <t>सीटी बजते ही</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>नमक की वजह से</t>
+          <t>भाप निकलने के बाद</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>तेल की वजह से</t>
+          <t>गैस चालू रखकर</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>हल्दी की वजह से</t>
+          <t>पानी डालकर</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>अंदर बनी भाप की वजह से</t>
+          <t>भाप निकलने के बाद</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -4344,32 +4344,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>दही जमाने के लिए दूध कैसा होना चाहिए?</t>
+          <t>फ्रिज में कच्चा-पका खाना अलग क्यों रखें?</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>एकदम ठंडा</t>
+          <t>जगह बचे</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>हल्का गुनगुना</t>
+          <t>ज़्यादा ठंडा रहे</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>खौलता हुआ</t>
+          <t>कीटाणु न फैलें</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>बर्फ जैसा</t>
+          <t>बिजली बचे</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>हल्का गुनगुना</t>
+          <t>कीटाणु न फैलें</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -4379,32 +4379,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>पालक उबालने के बाद ठंडे पानी में डालने से क्या फायदा होता है?</t>
+          <t>भूरे और सफेद छिलके वाले अंडे के पोषण में फर्क?</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>हरा रंग बना रहता है</t>
+          <t>भूरा दोगुना</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>स्वाद कड़वा होता है</t>
+          <t>लगभग कोई नहीं</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>पालक गल जाता है</t>
+          <t>सफेद दोगुना</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>कोई फायदा नहीं</t>
+          <t>भूरा नकली</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>हरा रंग बना रहता है</t>
+          <t>लगभग कोई नहीं</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -4414,32 +4414,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>कटे हुए आलू को पानी में क्यों रखते हैं?</t>
+          <t>एक ही तेल बार-बार गरम करना कैसा है?</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ताकि वे काले न पड़ें</t>
+          <t>फायदेमंद</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ताकि वे मीठे हो जाएँ</t>
+          <t>सेहत के लिए हानिकारक</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ताकि वे सख़्त हो जाएँ</t>
+          <t>स्वाद बढ़ाता है</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ताकि वे पक जाएँ</t>
+          <t>बिल्कुल ठीक</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ताकि वे काले न पड़ें</t>
+          <t>सेहत के लिए हानिकारक</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -4449,32 +4449,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>घर पर ओआरएस बनाने के लिए एक लीटर साफ पानी में क्या मिलाया जाता है?</t>
+          <t>बिजली का प्लग निकालते समय क्या पकड़ें?</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>सिर्फ़ चीनी</t>
+          <t>तार को</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>थोड़ी चीनी और चुटकी भर नमक</t>
+          <t>प्लग को</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>सिर्फ़ मसाला</t>
+          <t>स्विच को</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>सिर्फ़ तेल</t>
+          <t>दीवार को</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>थोड़ी चीनी और चुटकी भर नमक</t>
+          <t>प्लग को</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -4484,32 +4484,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>स्वस्थ इंसान के शरीर का सामान्य तापमान लगभग कितना होता है?</t>
+          <t>गीले हाथ से स्विच छूना खतरनाक क्यों है?</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>96.8° फ़ारेनहाइट</t>
+          <t>स्विच गरम होता है</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>98.6° फ़ारेनहाइट</t>
+          <t>स्विच टूटता है</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>100.4° फ़ारेनहाइट</t>
+          <t>पानी बिजली का सुचालक है</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>102.2° फ़ारेनहाइट</t>
+          <t>आवाज़ होती है</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>98.6° फ़ारेनहाइट</t>
+          <t>पानी बिजली का सुचालक है</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -4519,32 +4519,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>आयुष्मान भारत योजना में एक परिवार को सालाना कितने रुपये तक का इलाज मुफ़्त मिलता है?</t>
+          <t>500 ग्राम का पैकेट 60 रुपये का और 750 ग्राम का 84 रुपये का है। सस्ता कौन?</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>50 हज़ार</t>
+          <t>500 ग्राम वाला</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1 लाख</t>
+          <t>750 ग्राम वाला</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>5 लाख</t>
+          <t>दोनों बराबर</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>20 लाख</t>
+          <t>कहना मुश्किल</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>5 लाख</t>
+          <t>750 ग्राम वाला</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -4554,32 +4554,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>बैंक की पासबुक में क्या दर्ज होता है?</t>
+          <t>फोन चार्ज करते समय तकिये के नीचे रखने से?</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>खाते के लेन-देन का ब्योरा</t>
+          <t>आग का खतरा</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>घर का राशन</t>
+          <t>तेज़ चार्ज</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>बच्चों की फीस</t>
+          <t>आवाज़ बढ़ती</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>बिजली का बिल</t>
+          <t>स्क्रीन साफ़</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>खाते के लेन-देन का ब्योरा</t>
+          <t>आग का खतरा</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -4589,32 +4589,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>चेक के कोने पर दो आड़ी रेखाएँ खींचने का क्या मतलब होता है?</t>
+          <t>पैकेट पर हरे बिंदु का मतलब क्या है?</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>पैसा सीधे नकद मिलेगा</t>
+          <t>मीठा</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>पैसा सिर्फ़ खाते में जमा होगा</t>
+          <t>ताज़ा</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>चेक रद्द हो गया</t>
+          <t>शाकाहारी</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>चेक पुराना है</t>
+          <t>मुफ़्त</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>पैसा सिर्फ़ खाते में जमा होगा</t>
+          <t>शाकाहारी</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -4624,32 +4624,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>एटीएम मशीन में कार्ड फँस जाए तो सबसे पहले क्या करना चाहिए?</t>
+          <t>पैकेट पर 'बेस्ट बिफ़ोर' का मतलब क्या है?</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>किसी अजनबी की मदद लेना</t>
+          <t>इस तारीख को बना</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>बैंक की हेल्पलाइन पर बताकर कार्ड ब्लॉक कराना</t>
+          <t>इस तारीख तक सबसे अच्छी क्वालिटी</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>पिन बता देना</t>
+          <t>इस तारीख के बाद ज़हर</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>मशीन तोड़ना</t>
+          <t>इस तारीख तक मुफ़्त</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>बैंक की हेल्पलाइन पर बताकर कार्ड ब्लॉक कराना</t>
+          <t>इस तारीख तक सबसे अच्छी क्वालिटी</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -4659,32 +4659,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>बीमा या बैंक खाते में 'नॉमिनी' किसे कहते हैं?</t>
+          <t>पैकेट पर FSSAI के निशान का मतलब?</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>जिसे आपके बाद पैसा मिलेगा</t>
+          <t>खाद्य सुरक्षा मंज़ूरी</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>बैंक का मैनेजर</t>
+          <t>दुकान का नाम</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>पड़ोसी</t>
+          <t>वज़न</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>दुकानदार</t>
+          <t>कीमत</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>जिसे आपके बाद पैसा मिलेगा</t>
+          <t>खाद्य सुरक्षा मंज़ूरी</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -4694,32 +4694,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>सुकन्या समृद्धि खाता किसके नाम पर खुलता है?</t>
+          <t>पैकेट खरीदते समय सबसे ज़रूरी क्या देखें?</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>बेटी के नाम पर</t>
+          <t>पैकेट का रंग</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>पति के नाम पर</t>
+          <t>दुकान का नाम</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>दादा के नाम पर</t>
+          <t>एक्सपायरी डेट</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>पड़ोसी के नाम पर</t>
+          <t>पैकेट का आकार</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>बेटी के नाम पर</t>
+          <t>एक्सपायरी डेट</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -4729,32 +4729,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>उज्ज्वला योजना में गैस कनेक्शन किन्हें दिया जाता है?</t>
+          <t>सामान पर लिखे एमआरपी का मतलब?</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>गरीब परिवार की महिलाओं को</t>
+          <t>न्यूनतम मूल्य</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>सिर्फ़ अमीरों को</t>
+          <t>अधिकतम खुदरा मूल्य</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>सिर्फ़ दुकानदारों को</t>
+          <t>थोक दाम</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>सिर्फ़ विदेशियों को</t>
+          <t>छूट का दाम</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>गरीब परिवार की महिलाओं को</t>
+          <t>अधिकतम खुदरा मूल्य</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -4764,32 +4764,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>'मसालों की रानी' किसे कहा जाता है?</t>
+          <t>दुकानदार एमआरपी से ज़्यादा दाम माँगे तो?</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>इलायची</t>
+          <t>ठीक है</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>हल्दी</t>
+          <t>ज़रूरी है</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>जीरा</t>
+          <t>गलत है, मना कर सकते हैं</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>धनिया</t>
+          <t>कानूनी है</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>इलायची</t>
+          <t>गलत है, मना कर सकते हैं</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -4799,32 +4799,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>'मसालों का राजा' किसे कहा जाता है?</t>
+          <t>इडली-डोसा का घोल फूलने के लिए क्या ज़रूरी है?</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>काली मिर्च</t>
+          <t>ज़्यादा नमक</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>लौंग</t>
+          <t>ज़्यादा पानी</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>दालचीनी</t>
+          <t>तुरंत पकाना</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>हींग</t>
+          <t>कुछ घंटे रखकर खमीर उठना</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>काली मिर्च</t>
+          <t>कुछ घंटे रखकर खमीर उठना</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -4834,32 +4834,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>रसगुल्ला किससे बनता है?</t>
+          <t>तेल गरम हुआ या नहीं, कैसे परखें?</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>बेसन से</t>
+          <t>नमक डालकर</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>छेने (फटे दूध के पनीर) से</t>
+          <t>एक दाना जीरा डालकर</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>आटे से</t>
+          <t>पानी डालकर</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>चावल से</t>
+          <t>आटा डालकर</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>छेने (फटे दूध के पनीर) से</t>
+          <t>एक दाना जीरा डालकर</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -4869,32 +4869,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>पोहा किस चीज़ से बनता है?</t>
+          <t>टीवी रिमोट से बंद करने पर (स्टैंडबाय में) क्या होता है?</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>चावल को चपटा करके</t>
+          <t>बिल्कुल बिजली नहीं</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>गेहूँ से</t>
+          <t>थोड़ी बिजली खर्च होती रहती है</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>चने से</t>
+          <t>ज़्यादा बिजली खर्च</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>मक्के से</t>
+          <t>टीवी तेज़ चलता है</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>चावल को चपटा करके</t>
+          <t>थोड़ी बिजली खर्च होती रहती है</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -4904,32 +4904,32 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>सत्तू किस चीज़ से बनता है?</t>
+          <t>सब्ज़ी ज़्यादा खट्टी हो जाए तो क्या डालें?</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>भुने हुए चने या जौ से</t>
+          <t>ज़्यादा नमक</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>चावल से</t>
+          <t>पानी</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>मैदे से</t>
+          <t>चुटकी भर चीनी</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>सूजी से</t>
+          <t>मिर्च</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>भुने हुए चने या जौ से</t>
+          <t>चुटकी भर चीनी</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4939,32 +4939,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>रक्षाबंधन किस हिंदी महीने में आता है?</t>
+          <t>खिले-खिले चावल पकाने के लिए पहले क्या करें?</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>सावन (श्रावण)</t>
+          <t>भूनकर रखें</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>कार्तिक</t>
+          <t>भिगोकर रखें</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>फाल्गुन</t>
+          <t>फ्रिज में रखें</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>चैत्र</t>
+          <t>पीस लें</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>सावन (श्रावण)</t>
+          <t>भिगोकर रखें</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4974,32 +4974,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>होली किस महीने की पूर्णिमा को मनाई जाती है?</t>
+          <t>आटा 38 रुपये किलो है, तो ढाई किलो का दाम?</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>फाल्गुन</t>
+          <t>90 रुपये</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>श्रावण</t>
+          <t>95 रुपये</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>कार्तिक</t>
+          <t>100 रुपये</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>माघ</t>
+          <t>85 रुपये</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>फाल्गुन</t>
+          <t>95 रुपये</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -5009,32 +5009,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>नवरात्रि के बाद दसवें दिन कौन-सा त्योहार मनाया जाता है?</t>
+          <t>गीजर कब बंद कर देना चाहिए?</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>दशहरा</t>
+          <t>पानी गरम होते ही</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>होली</t>
+          <t>पूरे दिन चलाएँ</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>रक्षाबंधन</t>
+          <t>कभी नहीं</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>लोहड़ी</t>
+          <t>अगली सुबह</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>दशहरा</t>
+          <t>पानी गरम होते ही</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -5044,32 +5044,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>छठ पूजा कितने दिन चलती है?</t>
+          <t>500 रुपये के सामान पर 20% छूट, कितने देने होंगे?</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1 दिन</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2 दिन</t>
+          <t>350</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>4 दिन</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>10 दिन</t>
+          <t>450</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>4 दिन</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -5079,32 +5079,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>गणेशोत्सव सामान्यतः कितने दिन तक मनाया जाता है?</t>
+          <t>760 रुपये के बिल पर 1000 दिए, वापस कितने?</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3 दिन</t>
+          <t>230</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>5 दिन</t>
+          <t>240</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>10 दिन</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>21 दिन</t>
+          <t>260</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>10 दिन</t>
+          <t>240</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -5114,32 +5114,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ईद-उल-फ़ित्र किस महीने के रोज़ों के बाद मनाई जाती है?</t>
+          <t>साबुन से हाथ कम से कम कितनी देर धोने चाहिए?</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>रमज़ान</t>
+          <t>2 सेकंड</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>मुहर्रम</t>
+          <t>5 सेकंड</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>सावन</t>
+          <t>20 सेकंड</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>पौष</t>
+          <t>1 घंटा</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>रमज़ान</t>
+          <t>20 सेकंड</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -5149,32 +5149,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>गुड़ी पड़वा पर महाराष्ट्र में घर के बाहर क्या लगाया जाता है?</t>
+          <t>रोज़ पौन लीटर दूध आए तो 30 दिन में कितना?</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>गुड़ी (सजा हुआ ध्वज)</t>
+          <t>20 लीटर</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>पतंग</t>
+          <t>22.5 लीटर</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>तोरण के बजाय जाल</t>
+          <t>25 लीटर</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>झाड़ू</t>
+          <t>30 लीटर</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>गुड़ी (सजा हुआ ध्वज)</t>
+          <t>22.5 लीटर</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -5184,32 +5184,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>गुजरात की राजधानी कौन-सी है?</t>
+          <t>बिजली 6 रुपये यूनिट हो तो 90 यूनिट का बिल?</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>अहमदाबाद</t>
+          <t>450</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>गांधीनगर</t>
+          <t>540</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>सूरत</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>वडोदरा</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>गांधीनगर</t>
+          <t>540</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -5219,32 +5219,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>मध्य प्रदेश की राजधानी कौन-सी है?</t>
+          <t>दूध खराब है, यह कैसे पता चलता है?</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>इंदौर</t>
+          <t>मीठी गंध</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>जबलपुर</t>
+          <t>खट्टी गंध</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>भोपाल</t>
+          <t>गाढ़ापन</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ग्वालियर</t>
+          <t>ठंडा रहना</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>भोपाल</t>
+          <t>खट्टी गंध</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -5254,32 +5254,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>केरल की राजधानी कौन-सी है?</t>
+          <t>स्कूल बैग का वज़न बच्चे के वज़न का लगभग कितना हो?</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>कोच्चि</t>
+          <t>बराबर</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>तिरुवनंतपुरम</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>कोझिकोड</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>त्रिशूर</t>
+          <t>10% तक</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>तिरुवनंतपुरम</t>
+          <t>10% तक</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -5289,32 +5289,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>भारत में कुल कितने राज्य हैं?</t>
+          <t>गैस सिलेंडर की लीकेज जाँचने का सुरक्षित तरीका?</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>माचिस जलाना</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>साबुन का झागदार घोल</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>लाइटर जलाना</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>मोमबत्ती जलाना</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>साबुन का झागदार घोल</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -5324,32 +5324,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>तिरंगे के बीच के अशोक चक्र में कितनी तीलियाँ होती हैं?</t>
+          <t>इनमें कौन-सा नाम महिंद्रा की गाड़ी का नहीं है?</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>स्कॉर्पियो</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>बोलेरो</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>फॉर्च्यूनर</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>थार</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>फॉर्च्यूनर</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -5359,32 +5359,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>इनमें से कौन-सा नाम महिंद्रा की गाड़ी का नहीं है?</t>
+          <t>महिंद्रा थार में '4x4' का क्या मतलब है?</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>स्कॉर्पियो</t>
+          <t>चार दरवाज़े</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>एक्सयूवी700</t>
+          <t>चार सीटें</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>बोलेरो</t>
+          <t>चारों पहियों को ताकत</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>फॉर्च्यूनर</t>
+          <t>चार गियर</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>फॉर्च्यूनर</t>
+          <t>चारों पहियों को ताकत</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -5394,32 +5394,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>महिंद्रा थार को खासतौर पर किस रूप में जाना जाता है?</t>
+          <t>फैक्ट्री का हूटर आमतौर पर किसलिए बजता है?</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ऑफ-रोड एसयूवी</t>
+          <t>शिफ्ट बदलने या आपात सूचना के लिए</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>मिनी बस</t>
+          <t>गाना सुनाने के लिए</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>इलेक्ट्रिक स्कूटर</t>
+          <t>खाना बाँटने के लिए</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>सामान ढोने वाला ठेला</t>
+          <t>खेल शुरू करने के लिए</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>ऑफ-रोड एसयूवी</t>
+          <t>शिफ्ट बदलने या आपात सूचना के लिए</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -5429,32 +5429,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>स्वराज ट्रैक्टर किस ग्रुप का हिस्सा है?</t>
+          <t>महिंद्रा बीई 6 किससे चलती है?</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>महिंद्रा ग्रुप</t>
+          <t>पेट्रोल</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>टाटा ग्रुप</t>
+          <t>डीज़ल</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>बजाज ग्रुप</t>
+          <t>बैटरी</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>मारुति</t>
+          <t>गैस</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>महिंद्रा ग्रुप</t>
+          <t>बैटरी</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -5464,32 +5464,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>टेक महिंद्रा किस क्षेत्र की कंपनी है?</t>
+          <t>महिंद्रा रेसिंग किस तरह की रेस में उतरती है?</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>कपड़ा</t>
+          <t>बैलगाड़ी की</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>मिठाई</t>
+          <t>इलेक्ट्रिक कारों की</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>आईटी/सॉफ्टवेयर सेवाएँ</t>
+          <t>साइकिल की</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>जूते</t>
+          <t>नाव की</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>आईटी/सॉफ्टवेयर सेवाएँ</t>
+          <t>इलेक्ट्रिक कारों की</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -5499,32 +5499,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>महिंद्रा फाइनेंस से ट्रैक्टर या गाड़ी का लोन लेने पर हर महीने क्या चुकाना होता है?</t>
+          <t>महिंद्रा की फैक्ट्री में आपातकालीन निकास का निशान किस रंग का होता है?</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ईएमआई (किस्त)</t>
+          <t>लाल</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>राशन</t>
+          <t>पीला</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>बिजली का बिल</t>
+          <t>हरा</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>स्कूल की फीस</t>
+          <t>नीला</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ईएमआई (किस्त)</t>
+          <t>हरा</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -5534,22 +5534,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>महिंद्रा की 'प्रोजेक्ट नन्ही कली' किसके लिए काम करती है?</t>
+          <t>'नन्ही कली' किसके लिए काम करती है?</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
+          <t>किसानों के कर्ज़</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
           <t>बालिकाओं की शिक्षा</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>किसानों के कर्ज़</t>
-        </is>
-      </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>बुज़ुर्गों की पेंशन</t>
+          <t>पेंशन</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5569,32 +5569,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>'महिंद्रा हरियाली' पहल किस काम के लिए है?</t>
+          <t>महिंद्रा ट्रेओ क्या है?</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>पेड़ लगाने के लिए</t>
+          <t>ट्रैक्टर ट्रॉली</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>सड़क बनाने के लिए</t>
+          <t>हवाई जहाज़</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>खाना बाँटने के लिए</t>
+          <t>इलेक्ट्रिक ऑटो</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>कपड़े बाँटने के लिए</t>
+          <t>साइकिल</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>पेड़ लगाने के लिए</t>
+          <t>इलेक्ट्रिक ऑटो</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -5604,32 +5604,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>महिंद्रा ट्रेओ (Treo) क्या है?</t>
+          <t>'महिंद्रा हरियाली' किसके लिए है?</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>इलेक्ट्रिक तीन-पहिया ऑटो</t>
+          <t>सड़क बनाना</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ट्रैक्टर ट्रॉली</t>
+          <t>पेड़ लगाना</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>हवाई जहाज़</t>
+          <t>खाना बाँटना</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>साइकिल</t>
+          <t>कपड़े बाँटना</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>इलेक्ट्रिक तीन-पहिया ऑटो</t>
+          <t>पेड़ लगाना</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -5639,32 +5639,32 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>महिंद्रा जीतो (Jeeto) क्या है?</t>
+          <t>महिंद्रा ग्रुप लगभग कितने देशों में काम करता है?</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>छोटा मालवाहक वाहन</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>हवाई जहाज़</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>साइकिल</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>ट्रेन का डिब्बा</t>
+          <t>100 से ज़्यादा</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>छोटा मालवाहक वाहन</t>
+          <t>100 से ज़्यादा</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -5674,32 +5674,32 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>महिंद्रा रेसिंग किस तरह की रेस में हिस्सा लेती है?</t>
+          <t>महिंद्रा का हरिद्वार वाला कारखाना किस राज्य में है?</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>इलेक्ट्रिक कारों की फॉर्मूला ई रेस</t>
+          <t>उत्तराखंड</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>बैलगाड़ी की रेस</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>साइकिल की रेस</t>
+          <t>बिहार</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>दौड़ की मैराथन</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>इलेक्ट्रिक कारों की फॉर्मूला ई रेस</t>
+          <t>उत्तराखंड</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -5709,32 +5709,32 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>₹2400 की चीज़ पर 15% की छूट मिले तो कितने रुपये देने होंगे?</t>
+          <t>दाल के तड़के में हींग डालने का फायदा क्या माना जाता है?</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>पेट की गैस कम करना</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>रंग बदलना</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>दाल गाढ़ी करना</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>मिठास बढ़ाना</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>पेट की गैस कम करना</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -5744,32 +5744,32 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>आलू 30 रु/किलो के 3 किलो, प्याज 40 रु/किलो के 2 किलो और टमाटर 60 रु/किलो के डेढ़ किलो लिए, तो कुल कितना बिल बना?</t>
+          <t>पके हुए चावल को बाहर देर तक छोड़ने पर क्या खतरा है?</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>240 रुपये</t>
+          <t>चावल मीठा हो जाता है</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>250 रुपये</t>
+          <t>फूड पॉइज़निंग</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>260 रुपये</t>
+          <t>चावल कच्चा हो जाता है</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>270 रुपये</t>
+          <t>कोई खतरा नहीं</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>260 रुपये</t>
+          <t>फूड पॉइज़निंग</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -5779,32 +5779,32 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>दूध 56 रुपये लीटर है और रोज़ डेढ़ लीटर आता है, तो 30 दिन का खर्च कितना होगा?</t>
+          <t>आलू को फ्रिज में रखने से क्या होता है?</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2100 रुपये</t>
+          <t>हरा हो जाता है</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2520 रुपये</t>
+          <t>मीठा हो जाता है</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2800 रुपये</t>
+          <t>काला पड़ता है</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>3000 रुपये</t>
+          <t>सड़ जाता है</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2520 रुपये</t>
+          <t>मीठा हो जाता है</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -5814,32 +5814,32 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>महीने की कमाई 30,000 रुपये है और 20% बचत करनी है, तो कितने रुपये बचेंगे?</t>
+          <t>प्याज़-लहसुन को कहाँ रखना सही है?</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>हवादार सूखी जगह</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>पानी में</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>फ्रिज के डिब्बे में</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>धूप में</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>हवादार सूखी जगह</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -5849,32 +5849,32 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>10,000 रुपये पर 6% सालाना साधारण ब्याज से 3 साल का ब्याज कितना होगा?</t>
+          <t>आटा ज़्यादा दिन ताज़ा रखने के लिए क्या करें?</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>खुली थैली में रखें</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>हवाबंद डिब्बे में रखें</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>गीली जगह रखें</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>धूप में रखें</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>हवाबंद डिब्बे में रखें</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -5884,32 +5884,32 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>हर महीने 1500 रुपये की आरडी (RD) 2 साल तक भरें, तो ब्याज छोड़कर कुल कितने रुपये जमा होंगे?</t>
+          <t>इंडक्शन चूल्हे पर कौन-सा बर्तन चलता है?</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>सिर्फ़ ताँबे का</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>सिर्फ़ काँच का</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>सिर्फ़ मिट्टी का</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>जिस पर चुंबक चिपके</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>जिस पर चुंबक चिपके</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -5919,32 +5919,32 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>बिजली की 250 यूनिट 5 रुपये प्रति यूनिट के हिसाब से और 150 रुपये स्थायी शुल्क मिलाकर बिल कितना बनेगा?</t>
+          <t>मसाले किस तरह रखने चाहिए?</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>गीले बर्तन में</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>खुले में</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>सूखे हवाबंद डिब्बे में</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>पानी के पास</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>सूखे हवाबंद डिब्बे में</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -5954,32 +5954,32 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>बाइक 50 किमी प्रति लीटर चलती है और पेट्रोल 100 रुपये लीटर है, तो 200 किमी का पेट्रोल खर्च कितना होगा?</t>
+          <t>बरसात में नमक गीला क्यों हो जाता है?</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>200 रुपये</t>
+          <t>धूप के कारण</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>300 रुपये</t>
+          <t>हवा की नमी सोखने से</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>400 रुपये</t>
+          <t>चीनी मिलने से</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>500 रुपये</t>
+          <t>बर्तन के कारण</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>400 रुपये</t>
+          <t>हवा की नमी सोखने से</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -5989,32 +5989,32 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2 लोगों के लिए 250 ग्राम दाल लगती है, तो 8 लोगों के लिए कितनी दाल चाहिए?</t>
+          <t>फ्रिज को दीवार से कुछ दूरी पर क्यों रखें?</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>750 ग्राम</t>
+          <t>दिखावे के लिए</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>1 किलो</t>
+          <t>हवा निकलने और ठंडक के लिए</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>1.5 किलो</t>
+          <t>जगह बचाने के लिए</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2 किलो</t>
+          <t>रंग बचाने के लिए</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>1 किलो</t>
+          <t>हवा निकलने और ठंडक के लिए</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -6024,32 +6024,32 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>किसी चीज़ का दाम पहले 20% बढ़ा और फिर 20% घटा, तो अंत में दाम असली दाम से कैसा रहेगा?</t>
+          <t>बिजली की 1 यूनिट किसके बराबर होती है?</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>बिल्कुल बराबर</t>
+          <t>1 वाट-घंटा</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>4% कम</t>
+          <t>1 किलोवाट-घंटा</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4% ज़्यादा</t>
+          <t>1 मिनट बिजली</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>20% कम</t>
+          <t>10 किलोवाट</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>4% कम</t>
+          <t>1 किलोवाट-घंटा</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -6059,32 +6059,32 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>एक काम 4 लोग 6 दिन में करते हैं। वही काम 6 लोग कितने दिन में करेंगे?</t>
+          <t>5-स्टार रेटिंग वाले उपकरण की खासियत?</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3 दिन</t>
+          <t>ज़्यादा आवाज़</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>4 दिन</t>
+          <t>ज़्यादा वज़न</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>5 दिन</t>
+          <t>कम बिजली खपत</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>9 दिन</t>
+          <t>ज़्यादा रोशनी</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>4 दिन</t>
+          <t>कम बिजली खपत</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -6094,32 +6094,32 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>पर्दे के लिए साढ़े तीन मीटर कपड़ा 120 रुपये प्रति मीटर के हिसाब से लिया, तो कुल दाम कितना हुआ?</t>
+          <t>एसी किस तापमान पर रखने से बिजली बचती है?</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>360 रुपये</t>
+          <t>16 डिग्री</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>400 रुपये</t>
+          <t>18 डिग्री</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>420 रुपये</t>
+          <t>24-26 डिग्री</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>480 रुपये</t>
+          <t>10 डिग्री</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>420 रुपये</t>
+          <t>24-26 डिग्री</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -6129,32 +6129,32 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ईएमआई (EMI) का क्या मतलब है?</t>
+          <t>एक यूनिट बिजली में 10 वाट का एलईडी बल्ब लगभग कितने घंटे जलेगा?</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>हर महीने चुकाई जाने वाली तय किस्त</t>
+          <t>10 घंटे</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>मुफ़्त इनाम</t>
+          <t>100 घंटे</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>एक बार का टैक्स</t>
+          <t>1000 घंटे</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>बैंक की छुट्टी</t>
+          <t>1 घंटा</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>हर महीने चुकाई जाने वाली तय किस्त</t>
+          <t>100 घंटे</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -6164,32 +6164,32 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>फोन पर कोई खुद को बैंक कर्मचारी बताकर कार्ड नंबर या ओटीपी माँगे तो क्या करना चाहिए?</t>
+          <t>फ्रिज का दरवाज़ा बार-बार खोलने से क्या होता है?</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>तुरंत बता देना</t>
+          <t>बिजली ज़्यादा खर्च होती है</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>फोन काटकर बैंक की शाखा या आधिकारिक नंबर से पूछना</t>
+          <t>फ्रिज और ठंडा होता है</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>आधा नंबर बताना</t>
+          <t>बिजली बचती है</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>दोस्तों को बताना</t>
+          <t>खाना जल्दी पकता है</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>फोन काटकर बैंक की शाखा या आधिकारिक नंबर से पूछना</t>
+          <t>बिजली ज़्यादा खर्च होती है</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -6199,32 +6199,32 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>साइबर ठगी की शिकायत के लिए राष्ट्रीय हेल्पलाइन नंबर कौन-सा है?</t>
+          <t>एक्सटेंशन बोर्ड में कई भारी उपकरण लगाने से क्या खतरा है?</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>बिजली बचती है</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>उपकरण तेज़ चलते हैं</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>कुछ नहीं होता</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>ओवरलोड से आग का खतरा</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>ओवरलोड से आग का खतरा</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -6234,32 +6234,32 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>आरडी (RD) क्या होती है?</t>
+          <t>मोबाइल के लिए कौन-सा चार्जर सबसे सुरक्षित है?</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>हर महीने तय रकम जमा करके बचत करना</t>
+          <t>कंपनी का असली</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>एक बार में पूरा कर्ज़ लेना</t>
+          <t>सस्ता लोकल</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>बीमा का दावा</t>
+          <t>किसी का पुराना</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>बैंक का तोहफ़ा</t>
+          <t>टूटे तार वाला</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>हर महीने तय रकम जमा करके बचत करना</t>
+          <t>कंपनी का असली</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -6269,32 +6269,32 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>खाते में 'डेबिट' होने का क्या मतलब है?</t>
+          <t>सेल में 'अप टू 50% ऑफ' का क्या मतलब है?</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>खाते से पैसा कटना</t>
+          <t>हर चीज़ पर 50% छूट</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>खाते में पैसा आना</t>
+          <t>ज़्यादा से ज़्यादा 50% तक छूट</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>खाता बंद होना</t>
+          <t>50 रुपये की छूट</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>खाता खुलना</t>
+          <t>सब कुछ मुफ़्त</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>खाते से पैसा कटना</t>
+          <t>ज़्यादा से ज़्यादा 50% तक छूट</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -6304,32 +6304,32 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>सामान पर लिखे 'एमआरपी (MRP)' का क्या मतलब है?</t>
+          <t>पानी की टंकी की सफ़ाई कम से कम कितने समय में कराएँ?</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>अधिकतम खुदरा मूल्य</t>
+          <t>1 हफ्ते</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>न्यूनतम खुदरा मूल्य</t>
+          <t>6 महीने</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>थोक का दाम</t>
+          <t>5 साल</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>छूट का दाम</t>
+          <t>कभी नहीं</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>अधिकतम खुदरा मूल्य</t>
+          <t>6 महीने</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -6339,32 +6339,32 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>क्रेडिट कार्ड का बिल समय पर न भरने पर क्या होता है?</t>
+          <t>कमाई 30,000 रुपये है और 20% बचत करनी है, तो कितनी बचत होगी?</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>इनाम मिलता है</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ब्याज और जुर्माना लगता है</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>कार्ड दोगुना हो जाता है</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>कुछ नहीं होता</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>ब्याज और जुर्माना लगता है</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -6374,32 +6374,32 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>बीमा की 'प्रीमियम' का क्या मतलब है?</t>
+          <t>5 किलो आटा 190 रुपये का और 10 किलो 360 रुपये का है। प्रति किलो सस्ता कौन?</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>बीमा के लिए चुकाई जाने वाली रकम</t>
+          <t>5 किलो वाला</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>बीमे से मिलने वाला इनाम</t>
+          <t>10 किलो वाला</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>दुकान का डिस्काउंट</t>
+          <t>दोनों बराबर</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>बैंक का ब्याज</t>
+          <t>कहना मुश्किल</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>बीमा के लिए चुकाई जाने वाली रकम</t>
+          <t>10 किलो वाला</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -6409,32 +6409,32 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>बच्चे को दस्त होने पर ओआरएस के साथ सरकारी सलाह में और क्या दिया जाता है?</t>
+          <t>दूध 56 रुपये लीटर है, रोज़ डेढ़ लीटर आता है। 30 दिन का खर्च?</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ज़िंक</t>
+          <t>2100 रुपये</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>कॉफ़ी</t>
+          <t>2520 रुपये</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>चॉकलेट</t>
+          <t>2800 रुपये</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>तला खाना</t>
+          <t>3000 रुपये</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ज़िंक</t>
+          <t>2520 रुपये</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -6444,32 +6444,32 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>अचार, पापड़ और नमकीन में किस चीज़ की मात्रा ज़्यादा होने से ब्लड प्रेशर बढ़ सकता है?</t>
+          <t>बाइक 45 किमी/लीटर चलती है, पेट्रोल 100 रुपये लीटर। 270 किमी का खर्च?</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>नमक</t>
+          <t>500 रुपये</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>चीनी</t>
+          <t>550 रुपये</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>दूध</t>
+          <t>600 रुपये</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>पानी</t>
+          <t>650 रुपये</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>नमक</t>
+          <t>600 रुपये</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -6479,32 +6479,32 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>सामान्यतः एक स्वस्थ व्यक्ति को रोज़ कितना पानी पीना चाहिए?</t>
+          <t>1500 रुपये की चीज़ पर 10% और फिर 10% छूट मिले, तो कितने देने होंगे?</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>एक गिलास</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2 से 3 लीटर</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>10 लीटर</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>आधा गिलास</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2 से 3 लीटर</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -6514,32 +6514,32 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>सरकारी अस्पतालों में गर्भवती महिलाओं को मुफ़्त क्या दिया जाता है?</t>
+          <t>5000 रुपये का राशन 8% महँगा हो जाए तो कितने का होगा?</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>आयरन-फोलिक एसिड की गोलियाँ</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>चॉकलेट</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>कोल्ड ड्रिंक</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>पाउडर</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>आयरन-फोलिक एसिड की गोलियाँ</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -6549,32 +6549,32 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>घर में फ्यूज़ या एमसीबी का काम क्या होता है?</t>
+          <t>किसी चीज़ का दाम 500 से 600 रुपये हुआ, तो कितने प्रतिशत बढ़ा?</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ज़्यादा करंट आने पर बिजली अपने-आप काट देना</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>बिजली बढ़ाना</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>पंखा तेज़ करना</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>बल्ब जलाना</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>ज़्यादा करंट आने पर बिजली अपने-आप काट देना</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -6584,32 +6584,32 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>कढ़ाई के तेल में आग लग जाए तो सही तरीका क्या है?</t>
+          <t>दाम पहले 20% बढ़ा, फिर 20% घटा। अंत में असली दाम से कैसा?</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>पानी डालना</t>
+          <t>बराबर</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>गैस बंद करके ढक्कन से ढक देना</t>
+          <t>4% कम</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>फूँक मारना</t>
+          <t>4% ज़्यादा</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>कपड़े से हवा करना</t>
+          <t>20% कम</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>गैस बंद करके ढक्कन से ढक देना</t>
+          <t>4% कम</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -6619,32 +6619,32 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>एक्सपायरी डेट निकल चुकी दवा खानी चाहिए?</t>
+          <t>घर पर बनाया ओआरएस घोल कितने घंटे में इस्तेमाल कर लेना चाहिए?</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>हाँ, कुछ नहीं होता</t>
+          <t>5 मिनट</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>नहीं, फेंक देनी चाहिए</t>
+          <t>24 घंटे</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>आधी खा सकते हैं</t>
+          <t>1 हफ्ते</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>बच्चों को दे सकते हैं</t>
+          <t>1 महीने</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>नहीं, फेंक देनी चाहिए</t>
+          <t>24 घंटे</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -6654,32 +6654,32 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>हाथ जल जाने पर सबसे पहले क्या करना चाहिए?</t>
+          <t>एक काम 4 लोग 6 दिन में करते हैं। 6 लोग कितने दिन में करेंगे?</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>टूथपेस्ट लगाना</t>
+          <t>3 दिन</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>जले हिस्से पर ठंडा बहता पानी डालना</t>
+          <t>4 दिन</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>घी लगाना</t>
+          <t>5 दिन</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>आटा लगाना</t>
+          <t>9 दिन</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>जले हिस्से पर ठंडा बहता पानी डालना</t>
+          <t>4 दिन</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -6689,32 +6689,32 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>साँप के काटने पर सबसे पहले क्या करना चाहिए?</t>
+          <t>10,000 रुपये पर 6% सालाना साधारण ब्याज से 2 साल का ब्याज?</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>झाड़-फूँक करवाना</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>घबराए बिना तुरंत अस्पताल पहुँचना</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>घाव को मुँह से चूसना</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>इंतज़ार करना</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>घबराए बिना तुरंत अस्पताल पहुँचना</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -6724,32 +6724,32 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>स्वतंत्रता दिवस पर प्रधानमंत्री किस ऐतिहासिक जगह से तिरंगा फहराते हैं?</t>
+          <t>ज़्यादा शुद्ध सोना कौन-सा होता है?</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>लाल किला</t>
+          <t>22 कैरेट</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ताजमहल</t>
+          <t>18 कैरेट</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>कुतुब मीनार</t>
+          <t>24 कैरेट</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>इंडिया गेट</t>
+          <t>14 कैरेट</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>लाल किला</t>
+          <t>24 कैरेट</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -6759,32 +6759,32 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>गणतंत्र दिवस पर दिल्ली में तिरंगा कौन फहराता है?</t>
+          <t>बच्चे को दवा देने के लिए सबसे सही चीज़ क्या है?</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>प्रधानमंत्री</t>
+          <t>घर का चम्मच</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>राष्ट्रपति</t>
+          <t>अंदाज़ा</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री</t>
+          <t>नापने वाला ढक्कन या चम्मच</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>लोकसभा अध्यक्ष</t>
+          <t>हाथ</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>राष्ट्रपति</t>
+          <t>नापने वाला ढक्कन या चम्मच</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -6794,32 +6794,32 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>चारमीनार किस शहर में है?</t>
+          <t>सोने के गहने पर हॉलमार्क क्या बताता है?</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>हैदराबाद</t>
+          <t>शुद्धता</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>जयपुर</t>
+          <t>वज़न</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>लखनऊ</t>
+          <t>दुकान का नाम</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>भोपाल</t>
+          <t>पुरानापन</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>हैदराबाद</t>
+          <t>शुद्धता</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -6829,32 +6829,32 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>भारत का सबसे ऊँचा पर्वत शिखर कौन-सा है?</t>
+          <t>सामान पर आईएसआई निशान का मतलब?</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>एवरेस्ट</t>
+          <t>सस्ता</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>कंचनजंगा</t>
+          <t>विदेशी</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>नंदा देवी</t>
+          <t>गुणवत्ता मानक</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>के-2</t>
+          <t>पुराना</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>कंचनजंगा</t>
+          <t>गुणवत्ता मानक</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -6864,32 +6864,32 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>नीरज चोपड़ा किस खेल के खिलाड़ी हैं?</t>
+          <t>दवा की स्ट्रिप पर लाल खड़ी रेखा का क्या मतलब है?</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>भाला फेंक</t>
+          <t>मुफ़्त है</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>कुश्ती</t>
+          <t>पुरानी है</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>बैडमिंटन</t>
+          <t>मीठी है</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>क्रिकेट</t>
+          <t>डॉक्टर की पर्ची पर ही लें</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>भाला फेंक</t>
+          <t>डॉक्टर की पर्ची पर ही लें</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -6899,32 +6899,32 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>मैरी कॉम किस खेल की खिलाड़ी हैं?</t>
+          <t>नमक में आयोडीन किस रोग से बचाता है?</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>मुक्केबाज़ी</t>
+          <t>घेंघा</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>टेनिस</t>
+          <t>मलेरिया</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>हॉकी</t>
+          <t>टीबी</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>तीरंदाज़ी</t>
+          <t>पीलिया</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>मुक्केबाज़ी</t>
+          <t>घेंघा</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -6934,32 +6934,32 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>भारत की सबसे लंबी नदी कौन-सी मानी जाती है?</t>
+          <t>टोन्ड और फुल क्रीम दूध में क्या अंतर है?</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>यमुना</t>
+          <t>रंग</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>गंगा</t>
+          <t>फैट की मात्रा</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>नर्मदा</t>
+          <t>पानी का स्वाद</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>गोदावरी</t>
+          <t>पैकेट का आकार</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>गंगा</t>
+          <t>फैट की मात्रा</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -6969,32 +6969,32 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>क्षेत्रफल में भारत का सबसे बड़ा राज्य कौन-सा है?</t>
+          <t>एंटीबायोटिक दवा का क्या करना चाहिए?</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>राजस्थान</t>
+          <t>पूरा कोर्स लें</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश</t>
+          <t>आराम पर बंद करें</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>महाराष्ट्र</t>
+          <t>आधी लें</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>किसी को दें</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>राजस्थान</t>
+          <t>पूरा कोर्स लें</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -7004,32 +7004,32 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>तिरुपति बालाजी मंदिर किस राज्य में है?</t>
+          <t>आटा गूँथकर थोड़ी देर ढककर रखने से रोटी नरम क्यों बनती है?</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>आंध्र प्रदेश</t>
+          <t>आटा पानी सोखकर फूल जाता है</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>केरल</t>
+          <t>आटा जम जाता है</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>तेल बन जाता है</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>रंग बदल जाता है</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>आंध्र प्रदेश</t>
+          <t>आटा पानी सोखकर फूल जाता है</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -7039,32 +7039,32 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>वैष्णो देवी मंदिर किस राज्य/केंद्रशासित प्रदेश में है?</t>
+          <t>दवा 'दिन में दो बार' कैसे लें?</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>जम्मू-कश्मीर</t>
+          <t>एक साथ दोनों</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>हिमाचल प्रदेश</t>
+          <t>लगभग 12 घंटे के अंतर पर</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>उत्तराखंड</t>
+          <t>सिर्फ़ रात में</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>जब मन करे</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>जम्मू-कश्मीर</t>
+          <t>लगभग 12 घंटे के अंतर पर</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -7074,32 +7074,32 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>दिवाली के पाँच दिनों में धनतेरस के बाद अगला दिन कौन-सा होता है?</t>
+          <t>महिंद्रा का नासिक वाला कारखाना किस राज्य में है?</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>नरक चतुर्दशी (छोटी दिवाली)</t>
+          <t>महाराष्ट्र</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>भाई दूज</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>गोवर्धन पूजा</t>
+          <t>राजस्थान</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>दशहरा</t>
+          <t>बिहार</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>नरक चतुर्दशी (छोटी दिवाली)</t>
+          <t>महाराष्ट्र</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -7109,32 +7109,32 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>महिंद्रा एंड महिंद्रा की शुरुआत किस दशक में हुई थी?</t>
+          <t>महिंद्रा का ज़हीराबाद वाला कारखाना किस राज्य में है?</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>1920 का दशक</t>
+          <t>केरल</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>1940 का दशक</t>
+          <t>तेलंगाना</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>1960 का दशक</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>1980 का दशक</t>
+          <t>ओडिशा</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>1940 का दशक</t>
+          <t>तेलंगाना</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -7144,32 +7144,32 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>महिंद्रा स्कॉर्पियो पहली बार किस वर्ष आई थी?</t>
+          <t>दाल और चावल मिलाकर बनी खिचड़ी पौष्टिक क्यों मानी जाती है?</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>ज़्यादा चीनी</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>ज़्यादा तेल</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>प्रोटीन का बेहतर संतुलन</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>ज़्यादा नमक</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>प्रोटीन का बेहतर संतुलन</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -7179,32 +7179,32 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>इनमें से कौन-सी महिंद्रा की इलेक्ट्रिक एसयूवी है?</t>
+          <t>थार रॉक्स में आम थार से क्या ज़्यादा है?</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>नेक्सॉन ईवी</t>
+          <t>दो सीटें</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>बीई 6 (BE 6)</t>
+          <t>पाँच दरवाज़े</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>कर्व ईवी</t>
+          <t>तीन पहिये</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>टियागो ईवी</t>
+          <t>ट्रॉली</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>बीई 6 (BE 6)</t>
+          <t>पाँच दरवाज़े</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -7214,32 +7214,32 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>थार रॉक्स में आम थार के मुक़ाबले क्या ख़ास है?</t>
+          <t>महिंद्रा लाइफस्पेस क्या बनाती है?</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>पाँच दरवाज़े</t>
+          <t>बिस्कुट</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>दो पहिये</t>
+          <t>मकान और बिल्डिंग</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>सिर्फ़ एक सीट</t>
+          <t>मोबाइल</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>पूरी तरह खुली छत</t>
+          <t>साइकिल</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>पाँच दरवाज़े</t>
+          <t>मकान और बिल्डिंग</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -7249,32 +7249,32 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ट्रैक्टर के पीछे जुड़ने वाला रोटावेटर क्या काम करता है?</t>
+          <t>गाड़ी की फैक्ट्री में 'पेंट शॉप' का काम क्या होता है?</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>खेत की मिट्टी को भुरभुरी करता है</t>
+          <t>इंजन लगाना</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>फसल बेचता है</t>
+          <t>गाड़ी की बॉडी को रंगना</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>बीज पैक करता है</t>
+          <t>टायर बेचना</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>कपड़े धोता है</t>
+          <t>गाड़ी चलाना</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>खेत की मिट्टी को भुरभुरी करता है</t>
+          <t>गाड़ी की बॉडी को रंगना</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -7284,32 +7284,32 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>महिंद्रा लॉजिस्टिक्स मुख्य रूप से क्या काम करती है?</t>
+          <t>महिंद्रा ने जिस रेवा कंपनी को खरीदा, वह क्या बनाती थी?</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>माल ढुलाई और सप्लाई चेन</t>
+          <t>ट्रैक्टर</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>मिठाई बनाना</t>
+          <t>इलेक्ट्रिक कार</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>कपड़े सिलना</t>
+          <t>साइकिल</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>स्कूल चलाना</t>
+          <t>पंखे</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>माल ढुलाई और सप्लाई चेन</t>
+          <t>इलेक्ट्रिक कार</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -7319,32 +7319,32 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>महिंद्रा रिसर्च वैली किस शहर के पास है?</t>
+          <t>महिंद्रा ने भारत में जीप किस कंपनी की मदद से शुरू की?</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>चेन्नई</t>
+          <t>फ़ोर्ड</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>जयपुर</t>
+          <t>टोयोटा</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>लखनऊ</t>
+          <t>विलीज़</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>पटना</t>
+          <t>सुज़ुकी</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>चेन्नई</t>
+          <t>विलीज़</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -7354,32 +7354,32 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>महिंद्रा ने किस इलेक्ट्रिक कार कंपनी का अधिग्रहण किया था?</t>
+          <t>महिंद्रा ट्रैक्टर ने शुरुआत में किस विदेशी कंपनी से साझेदारी की?</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>रेवा (Reva)</t>
+          <t>फ़ोर्ड</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>टेस्ला</t>
+          <t>इंटरनेशनल हार्वेस्टर</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>नैनो</t>
+          <t>टोयोटा</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>बजाज</t>
+          <t>सैमसंग</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>रेवा (Reva)</t>
+          <t>इंटरनेशनल हार्वेस्टर</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -7389,32 +7389,32 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>गाड़ी की क्रैश-सुरक्षा (टक्कर में सुरक्षा) की रेटिंग किस तरह के टेस्ट से दी जाती है?</t>
+          <t>फैक्ट्री में 'वेल्डिंग' का क्या मतलब है?</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>एनसीएपी (NCAP) क्रैश टेस्ट</t>
+          <t>रंग करना</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>चाय का टेस्ट</t>
+          <t>पानी भरना</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>दौड़ का टेस्ट</t>
+          <t>धातु को गरम करके जोड़ना</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>रंग का टेस्ट</t>
+          <t>गाड़ी धोना</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>एनसीएपी (NCAP) क्रैश टेस्ट</t>
+          <t>धातु को गरम करके जोड़ना</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -7424,32 +7424,32 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>महिंद्रा ने शुरुआत में किस कंपनी के लाइसेंस से जीप बनाना शुरू किया था?</t>
+          <t>फैक्ट्री में 'असेंबली लाइन' का क्या मतलब है?</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>विलीज़ (Willys)</t>
+          <t>गाड़ी बेचना</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>फ़ोर्ड</t>
+          <t>गाड़ी धोना</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>टोयोटा</t>
+          <t>गाड़ी चलाना</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>सुज़ुकी</t>
+          <t>पुर्ज़े जोड़कर गाड़ी बनाना</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>विलीज़ (Willys)</t>
+          <t>पुर्ज़े जोड़कर गाड़ी बनाना</t>
         </is>
       </c>
       <c r="G201" t="n">
